--- a/tasks/finalpool/arxiv-research-tracker-notion/groundtruth_workspace/Transformer_Research_Tracker.xlsx
+++ b/tasks/finalpool/arxiv-research-tracker-notion/groundtruth_workspace/Transformer_Research_Tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,142 +430,232 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Authors</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Published_Date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Citation_Count</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Venue</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Primary_Category</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Key_Contribution</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2402.10001</t>
+          <t>2402.10003</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FlashAttention-3: Fast and Memory-Efficient Attention with IO-Awareness</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>520</v>
+          <t>LoRA: Low-Rank Adaptation of Large Language Models</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Edward Hu, Yelong Shen, Phillip Wallis</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>cs.LG</t>
+          <t>ICLR</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>cs.CL</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Proposes low-rank adaptation method that drastically reduces parameters for fine-tuning large language models.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2402.10002</t>
+          <t>2402.10001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Efficient Transformers via Token Merging and Pruning</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>180</v>
+          <t>FlashAttention-3: Fast and Memory-Efficient Attention with IO-Awareness</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Tri Dao, Albert Gu</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>cs.CV</t>
+          <t>NeurIPS</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>520</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>cs.LG</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Introduces IO-aware attention computation achieving faster and memory-efficient transformer training.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2402.10003</t>
+          <t>2402.10005</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LoRA: Low-Rank Adaptation of Large Language Models</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1200</v>
+          <t>Sparse Mixture of Experts for Scalable Transformer Models</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Noam Shazeer, Barret Zoph</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>cs.CL</t>
+          <t>JMLR</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>340</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>cs.AI</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Scales transformer capacity via conditional computation using sparse mixture of experts layers.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2402.10004</t>
+          <t>2402.10002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quantization-Aware Training for Efficient Transformer Inference</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>95</v>
+          <t>Efficient Transformers via Token Merging and Pruning</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Daniel Bolya, Judy Hoffman</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ICML</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>cs.LG</t>
+          <t>ICLR</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>180</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>cs.CV</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Accelerates transformer inference by progressively merging and pruning redundant tokens.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2402.10005</t>
+          <t>2402.10004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sparse Mixture of Experts for Scalable Transformer Models</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>340</v>
+          <t>Quantization-Aware Training for Efficient Transformer Inference</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Markus Nagel, Mart van Baalen</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JMLR</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>cs.AI</t>
+          <t>ICML</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>95</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>cs.LG</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Enables low-bit quantization of transformers while preserving accuracy during inference.</t>
         </is>
       </c>
     </row>

--- a/tasks/finalpool/arxiv-research-tracker-notion/groundtruth_workspace/Transformer_Research_Tracker.xlsx
+++ b/tasks/finalpool/arxiv-research-tracker-notion/groundtruth_workspace/Transformer_Research_Tracker.xlsx
@@ -472,12 +472,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Edward Hu, Yelong Shen, Phillip Wallis</t>
+          <t>Edward Hu, Yelong Shen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024-02-18</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -495,7 +495,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Proposes low-rank adaptation method that drastically reduces parameters for fine-tuning large language models.</t>
+          <t>Freezes pretrained weights and injects trainable low-rank matrices, cutting trainable parameters by 10,000x for GPT-3 175B with no inference latency.</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tri Dao, Albert Gu</t>
+          <t>Tri Dao, Daniel Fu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Introduces IO-aware attention computation achieving faster and memory-efficient transformer training.</t>
+          <t>Introduces IO-aware attention with asynchronous block-wise computation and improved memory tiling, achieving 2.1x speedup over FlashAttention-2 and enabling 128K-token training.</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Noam Shazeer, Barret Zoph</t>
+          <t>William Fedus, Jeff Dean</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Scales transformer capacity via conditional computation using sparse mixture of experts layers.</t>
+          <t>Replaces dense FFN layers with sparsely-activated expert layers routed by a learned gating mechanism, scaling capacity 8-64x at constant compute.</t>
         </is>
       </c>
     </row>
@@ -592,12 +592,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Daniel Bolya, Judy Hoffman</t>
+          <t>Daniel Bolya, Cheng-Yang Fu</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Accelerates transformer inference by progressively merging and pruning redundant tokens.</t>
+          <t>Accelerates vision transformers via combined token merging and pruning, reducing tokens by up to 60% with accuracy within 0.3% on ImageNet.</t>
         </is>
       </c>
     </row>
@@ -632,12 +632,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Markus Nagel, Mart van Baalen</t>
+          <t>Jianlin Su, Minjia Zhang</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Enables low-bit quantization of transformers while preserving accuracy during inference.</t>
+          <t>Quantization-aware training with learnable step sizes and mixed-precision (4-bit weights, 8-bit activations), reducing model size 4x within 0.5 perplexity.</t>
         </is>
       </c>
     </row>
